--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ83"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130302241</v>
+        <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,42 +1276,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445762</v>
+        <v>445645</v>
       </c>
       <c r="R7" t="n">
-        <v>7026257</v>
+        <v>7026372</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,27 +1330,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,13 +1371,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302241</t>
+          <t>https://artportalen.se/Sighting/136876232</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130302477</v>
+        <v>130302241</v>
       </c>
       <c r="B8" t="n">
         <v>91909</v>
@@ -1416,19 +1406,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445700</v>
+        <v>445762</v>
       </c>
       <c r="R8" t="n">
-        <v>7026308</v>
+        <v>7026257</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1492,19 +1487,19 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302477</t>
+          <t>https://artportalen.se/Sighting/130302241</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130303378</v>
+        <v>130302477</v>
       </c>
       <c r="B9" t="n">
         <v>91909</v>
@@ -1539,13 +1534,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445813</v>
+        <v>445700</v>
       </c>
       <c r="R9" t="n">
-        <v>7026366</v>
+        <v>7026308</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,27 +1599,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303378</t>
+          <t>https://artportalen.se/Sighting/130302477</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130838040</v>
+        <v>130303378</v>
       </c>
       <c r="B10" t="n">
-        <v>83312</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445709</v>
+        <v>445813</v>
       </c>
       <c r="R10" t="n">
-        <v>7026357</v>
+        <v>7026366</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,27 +1681,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,38 +1727,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838040</t>
+          <t>https://artportalen.se/Sighting/130303378</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130301433</v>
+        <v>130838040</v>
       </c>
       <c r="B11" t="n">
-        <v>79798</v>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1797</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445678</v>
+        <v>445709</v>
       </c>
       <c r="R11" t="n">
-        <v>7026239</v>
+        <v>7026357</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,27 +1798,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,49 +1833,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301433</t>
+          <t>https://artportalen.se/Sighting/130838040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130301943</v>
+        <v>130301433</v>
       </c>
       <c r="B12" t="n">
-        <v>80433</v>
+        <v>79798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1797</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1890,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445762</v>
+        <v>445678</v>
       </c>
       <c r="R12" t="n">
-        <v>7026257</v>
+        <v>7026239</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,44 +1955,44 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301943</t>
+          <t>https://artportalen.se/Sighting/130301433</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130302348</v>
+        <v>130301943</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2007,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445688</v>
+        <v>445762</v>
       </c>
       <c r="R13" t="n">
-        <v>7026324</v>
+        <v>7026257</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2047,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,44 +2072,44 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302348</t>
+          <t>https://artportalen.se/Sighting/130301943</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130300161</v>
+        <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>93083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2124,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445826</v>
+        <v>445723</v>
       </c>
       <c r="R14" t="n">
-        <v>7026362</v>
+        <v>7026207</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,22 +2149,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,44 +2184,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300161</t>
+          <t>https://artportalen.se/Sighting/136875897</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130300210</v>
+        <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>93083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,13 +2231,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445816</v>
+        <v>445681</v>
       </c>
       <c r="R15" t="n">
-        <v>7026366</v>
+        <v>7026211</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2266,27 +2261,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,74 +2291,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300210</t>
+          <t>https://artportalen.se/Sighting/136875941</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130300326</v>
+        <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445796</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026382</v>
+        <v>7026345</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,27 +2373,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,74 +2403,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300326</t>
+          <t>https://artportalen.se/Sighting/136876113</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130300508</v>
+        <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>93083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445754</v>
+        <v>445714</v>
       </c>
       <c r="R17" t="n">
-        <v>7026380</v>
+        <v>7026372</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2518,27 +2485,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,74 +2515,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300508</t>
+          <t>https://artportalen.se/Sighting/136876614</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130300764</v>
+        <v>130302348</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445754</v>
+        <v>445688</v>
       </c>
       <c r="R18" t="n">
-        <v>7026359</v>
+        <v>7026324</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2649,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2659,12 +2612,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal död gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,19 +2637,19 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300764</t>
+          <t>https://artportalen.se/Sighting/130302348</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130300940</v>
+        <v>130300161</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2724,29 +2677,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445746</v>
+        <v>445826</v>
       </c>
       <c r="R19" t="n">
-        <v>7026325</v>
+        <v>7026362</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2775,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2785,12 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,24 +2744,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300940</t>
+          <t>https://artportalen.se/Sighting/130300161</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130301011</v>
+        <v>130300210</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2857,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445774</v>
+        <v>445816</v>
       </c>
       <c r="R20" t="n">
-        <v>7026314</v>
+        <v>7026366</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2890,9 +2829,24 @@
           <t>2025-12-26</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,24 +2861,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301011</t>
+          <t>https://artportalen.se/Sighting/130300210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130301029</v>
+        <v>130300326</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2954,7 +2908,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2968,10 +2922,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445739</v>
+        <v>445796</v>
       </c>
       <c r="R21" t="n">
-        <v>7026313</v>
+        <v>7026382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,12 +2967,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3038,19 +2992,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301029</t>
+          <t>https://artportalen.se/Sighting/130300326</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130301089</v>
+        <v>130300508</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3078,17 +3032,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445726</v>
+        <v>445754</v>
       </c>
       <c r="R22" t="n">
-        <v>7026295</v>
+        <v>7026380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,7 +3083,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3130,12 +3093,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,13 +3124,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301089</t>
+          <t>https://artportalen.se/Sighting/130300508</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130301166</v>
+        <v>130300764</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3197,7 +3160,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3211,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445711</v>
+        <v>445754</v>
       </c>
       <c r="R23" t="n">
-        <v>7026280</v>
+        <v>7026359</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3246,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3256,12 +3219,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3276,24 +3239,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301166</t>
+          <t>https://artportalen.se/Sighting/130300764</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130301447</v>
+        <v>130300940</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3337,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445671</v>
+        <v>445746</v>
       </c>
       <c r="R24" t="n">
-        <v>7026257</v>
+        <v>7026325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3372,7 +3335,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,12 +3345,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,13 +3376,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301447</t>
+          <t>https://artportalen.se/Sighting/130300940</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130301787</v>
+        <v>130301011</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3447,29 +3410,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445675</v>
+        <v>445774</v>
       </c>
       <c r="R25" t="n">
-        <v>7026220</v>
+        <v>7026314</v>
       </c>
       <c r="S25" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3496,24 +3450,9 @@
           <t>2025-12-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,24 +3467,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301787</t>
+          <t>https://artportalen.se/Sighting/130301011</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130302606</v>
+        <v>130301029</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3573,17 +3512,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445694</v>
+        <v>445739</v>
       </c>
       <c r="R26" t="n">
-        <v>7026212</v>
+        <v>7026313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3615,7 +3563,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3625,12 +3573,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3656,13 +3604,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302606</t>
+          <t>https://artportalen.se/Sighting/130301029</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130302719</v>
+        <v>130301089</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3697,10 +3645,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445708</v>
+        <v>445726</v>
       </c>
       <c r="R27" t="n">
-        <v>7026207</v>
+        <v>7026295</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3732,7 +3680,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3742,12 +3690,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3773,13 +3721,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302719</t>
+          <t>https://artportalen.se/Sighting/130301089</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130302963</v>
+        <v>130301166</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3809,7 +3757,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3823,13 +3771,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445703</v>
+        <v>445711</v>
       </c>
       <c r="R28" t="n">
-        <v>7026235</v>
+        <v>7026280</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3858,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3868,12 +3816,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3899,13 +3847,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302963</t>
+          <t>https://artportalen.se/Sighting/130301166</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130303237</v>
+        <v>130301447</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3935,7 +3883,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3949,10 +3897,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445744</v>
+        <v>445671</v>
       </c>
       <c r="R29" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3984,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3994,12 +3942,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4025,13 +3973,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303237</t>
+          <t>https://artportalen.se/Sighting/130301447</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303417</v>
+        <v>130301787</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -4061,7 +4009,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4075,13 +4023,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445827</v>
+        <v>445675</v>
       </c>
       <c r="R30" t="n">
-        <v>7026371</v>
+        <v>7026220</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4110,7 +4058,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4120,12 +4068,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4151,13 +4099,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303417</t>
+          <t>https://artportalen.se/Sighting/130301787</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130719248</v>
+        <v>130302606</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4185,29 +4133,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445790</v>
+        <v>445694</v>
       </c>
       <c r="R31" t="n">
-        <v>7026392</v>
+        <v>7026212</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4231,27 +4170,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4262,21 +4201,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4292,13 +4216,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719248</t>
+          <t>https://artportalen.se/Sighting/130302606</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130719350</v>
+        <v>130302719</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4326,26 +4250,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445746</v>
+        <v>445708</v>
       </c>
       <c r="R32" t="n">
-        <v>7026368</v>
+        <v>7026207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4372,27 +4287,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Draperat på 200-årig gammal levande gran i gammal granskog, längsta bål 60 cm</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4403,21 +4318,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4433,13 +4333,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719350</t>
+          <t>https://artportalen.se/Sighting/130302719</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130719426</v>
+        <v>130302963</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4467,20 +4367,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445709</v>
+        <v>445703</v>
       </c>
       <c r="R33" t="n">
-        <v>7026371</v>
+        <v>7026235</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4504,27 +4413,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal levande gran (42 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4550,13 +4459,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719426</t>
+          <t>https://artportalen.se/Sighting/130302963</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130719742</v>
+        <v>130303237</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4586,7 +4495,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4600,10 +4509,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445734</v>
+        <v>445744</v>
       </c>
       <c r="R34" t="n">
-        <v>7026264</v>
+        <v>7026231</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4630,27 +4539,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4676,13 +4585,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719742</t>
+          <t>https://artportalen.se/Sighting/130303237</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130719759</v>
+        <v>130303417</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4712,7 +4621,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4726,13 +4635,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445728</v>
+        <v>445827</v>
       </c>
       <c r="R35" t="n">
-        <v>7026253</v>
+        <v>7026371</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4756,27 +4665,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>40 bålar på 200-årig tall i gles gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4787,21 +4696,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4817,13 +4711,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719759</t>
+          <t>https://artportalen.se/Sighting/130303417</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130719818</v>
+        <v>130719248</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4853,7 +4747,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4867,13 +4761,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445747</v>
+        <v>445790</v>
       </c>
       <c r="R36" t="n">
-        <v>7026270</v>
+        <v>7026392</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4902,7 +4796,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4912,12 +4806,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (24 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4928,6 +4822,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4943,13 +4852,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719818</t>
+          <t>https://artportalen.se/Sighting/130719248</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130719892</v>
+        <v>130719350</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4979,7 +4888,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4993,10 +4902,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445759</v>
+        <v>445746</v>
       </c>
       <c r="R37" t="n">
-        <v>7026307</v>
+        <v>7026368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5028,7 +4937,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5038,12 +4947,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1000 bålar fördelat på 10 gamla granar i gammal granskog, längsta bållängd 70 cm</t>
+          <t>Draperat på 200-årig gammal levande gran i gammal granskog, längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5054,6 +4963,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5069,13 +4993,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719892</t>
+          <t>https://artportalen.se/Sighting/130719350</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130719929</v>
+        <v>130719426</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -5103,29 +5027,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445789</v>
+        <v>445709</v>
       </c>
       <c r="R38" t="n">
-        <v>7026327</v>
+        <v>7026371</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5154,7 +5069,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5164,12 +5079,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran (42 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5195,13 +5110,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719929</t>
+          <t>https://artportalen.se/Sighting/130719426</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130837289</v>
+        <v>130719742</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -5231,7 +5146,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5245,13 +5160,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445777</v>
+        <v>445734</v>
       </c>
       <c r="R39" t="n">
-        <v>7026331</v>
+        <v>7026264</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5275,27 +5190,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5321,13 +5236,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837289</t>
+          <t>https://artportalen.se/Sighting/130719742</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130837393</v>
+        <v>130719759</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5357,7 +5272,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5371,13 +5286,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445769</v>
+        <v>445728</v>
       </c>
       <c r="R40" t="n">
-        <v>7026332</v>
+        <v>7026253</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5401,27 +5316,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
+          <t>40 bålar på 200-årig tall i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,6 +5347,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5447,13 +5377,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837393</t>
+          <t>https://artportalen.se/Sighting/130719759</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130837733</v>
+        <v>130719818</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5481,17 +5411,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445720</v>
+        <v>445747</v>
       </c>
       <c r="R41" t="n">
-        <v>7026343</v>
+        <v>7026270</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5518,27 +5457,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal död gran i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (24 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5564,13 +5503,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837733</t>
+          <t>https://artportalen.se/Sighting/130719818</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130838099</v>
+        <v>130719892</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5598,20 +5537,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445679</v>
+        <v>445759</v>
       </c>
       <c r="R42" t="n">
-        <v>7026381</v>
+        <v>7026307</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5635,27 +5583,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>1000 bålar fördelat på 10 gamla granar i gammal granskog, längsta bållängd 70 cm</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5681,13 +5629,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838099</t>
+          <t>https://artportalen.se/Sighting/130719892</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130838225</v>
+        <v>130719929</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5715,20 +5663,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445632</v>
+        <v>445789</v>
       </c>
       <c r="R43" t="n">
-        <v>7026388</v>
+        <v>7026327</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5752,27 +5709,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gles skog nära källa</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5798,13 +5755,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838225</t>
+          <t>https://artportalen.se/Sighting/130719929</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130838554</v>
+        <v>130837289</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5832,20 +5789,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445665</v>
+        <v>445777</v>
       </c>
       <c r="R44" t="n">
-        <v>7026277</v>
+        <v>7026331</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5874,7 +5840,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5884,12 +5850,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal levande gran i björkrik granskog</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5915,13 +5881,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838554</t>
+          <t>https://artportalen.se/Sighting/130837289</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130838768</v>
+        <v>130837393</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5949,20 +5915,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445697</v>
+        <v>445769</v>
       </c>
       <c r="R45" t="n">
-        <v>7026283</v>
+        <v>7026332</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5991,7 +5966,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6001,12 +5976,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6032,13 +6007,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838768</t>
+          <t>https://artportalen.se/Sighting/130837393</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130838918</v>
+        <v>130837733</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -6073,13 +6048,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445653</v>
+        <v>445720</v>
       </c>
       <c r="R46" t="n">
-        <v>7026235</v>
+        <v>7026343</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6108,7 +6083,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6118,12 +6093,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal levande gran (ca 200 år) i gammal granskog</t>
+          <t>På gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6149,13 +6124,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838918</t>
+          <t>https://artportalen.se/Sighting/130837733</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130839080</v>
+        <v>130838099</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -6190,13 +6165,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445706</v>
+        <v>445679</v>
       </c>
       <c r="R47" t="n">
-        <v>7026203</v>
+        <v>7026381</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6225,7 +6200,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6235,12 +6210,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6266,13 +6241,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839080</t>
+          <t>https://artportalen.se/Sighting/130838099</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130839110</v>
+        <v>130838225</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -6300,29 +6275,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445730</v>
+        <v>445632</v>
       </c>
       <c r="R48" t="n">
-        <v>7026205</v>
+        <v>7026388</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6351,7 +6317,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6361,12 +6327,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal klen död gran i gammal granskog</t>
+          <t>På gammal gran i gles skog nära källa</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6392,13 +6358,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839110</t>
+          <t>https://artportalen.se/Sighting/130838225</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130839277</v>
+        <v>130838554</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -6426,29 +6392,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445728</v>
+        <v>445665</v>
       </c>
       <c r="R49" t="n">
-        <v>7026301</v>
+        <v>7026277</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6477,7 +6434,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6487,12 +6444,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i björkrik granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6518,13 +6475,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839277</t>
+          <t>https://artportalen.se/Sighting/130838554</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130839350</v>
+        <v>130838768</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6559,13 +6516,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445790</v>
+        <v>445697</v>
       </c>
       <c r="R50" t="n">
-        <v>7026340</v>
+        <v>7026283</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,7 +6551,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6604,12 +6561,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6635,13 +6592,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839350</t>
+          <t>https://artportalen.se/Sighting/130838768</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130839371</v>
+        <v>130838918</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6669,29 +6626,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445780</v>
+        <v>445653</v>
       </c>
       <c r="R51" t="n">
-        <v>7026357</v>
+        <v>7026235</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6720,7 +6668,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6730,12 +6678,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gles gammal granskog</t>
+          <t>På gammal levande gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6761,13 +6709,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839371</t>
+          <t>https://artportalen.se/Sighting/130838918</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130839417</v>
+        <v>130839080</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6802,13 +6750,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445781</v>
+        <v>445706</v>
       </c>
       <c r="R52" t="n">
-        <v>7026373</v>
+        <v>7026203</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6837,7 +6785,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6847,12 +6795,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6878,54 +6826,63 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839417</t>
+          <t>https://artportalen.se/Sighting/130839080</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130300852</v>
+        <v>130839110</v>
       </c>
       <c r="B53" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445737</v>
+        <v>445730</v>
       </c>
       <c r="R53" t="n">
-        <v>7026346</v>
+        <v>7026205</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6949,27 +6906,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal klen död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6995,54 +6952,63 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300852</t>
+          <t>https://artportalen.se/Sighting/130839110</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130837541</v>
+        <v>130839277</v>
       </c>
       <c r="B54" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445740</v>
+        <v>445728</v>
       </c>
       <c r="R54" t="n">
-        <v>7026322</v>
+        <v>7026301</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7071,7 +7037,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7081,12 +7047,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På tunna kvistar vid basen på gammal levande gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7112,38 +7078,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837541</t>
+          <t>https://artportalen.se/Sighting/130839277</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130301741</v>
+        <v>130839350</v>
       </c>
       <c r="B55" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7153,13 +7119,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445718</v>
+        <v>445790</v>
       </c>
       <c r="R55" t="n">
-        <v>7026281</v>
+        <v>7026340</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7183,27 +7149,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7218,62 +7184,71 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301741</t>
+          <t>https://artportalen.se/Sighting/130839350</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130302583</v>
+        <v>130839371</v>
       </c>
       <c r="B56" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445687</v>
+        <v>445780</v>
       </c>
       <c r="R56" t="n">
-        <v>7026235</v>
+        <v>7026357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7300,27 +7275,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran (ca 200 år) i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7346,38 +7321,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302583</t>
+          <t>https://artportalen.se/Sighting/130839371</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130837316</v>
+        <v>130839417</v>
       </c>
       <c r="B57" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7387,13 +7362,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445777</v>
+        <v>445781</v>
       </c>
       <c r="R57" t="n">
-        <v>7026331</v>
+        <v>7026373</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7422,7 +7397,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7432,12 +7407,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7463,38 +7438,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837316</t>
+          <t>https://artportalen.se/Sighting/130839417</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130837548</v>
+        <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>83307</v>
+        <v>79476</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7504,13 +7479,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445740</v>
+        <v>445645</v>
       </c>
       <c r="R58" t="n">
-        <v>7026322</v>
+        <v>7026372</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7534,27 +7509,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7569,65 +7539,74 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837548</t>
+          <t>https://artportalen.se/Sighting/136876260</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130838158</v>
+        <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>83307</v>
+        <v>79476</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445638</v>
+        <v>445636</v>
       </c>
       <c r="R59" t="n">
-        <v>7026382</v>
+        <v>7026394</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7651,27 +7630,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog, nära källa</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7686,65 +7660,74 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838158</t>
+          <t>https://artportalen.se/Sighting/136876308</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130839071</v>
+        <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>83307</v>
+        <v>79476</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445706</v>
+        <v>445631</v>
       </c>
       <c r="R60" t="n">
-        <v>7026203</v>
+        <v>7026386</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7768,27 +7751,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7803,49 +7786,49 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839071</t>
+          <t>https://artportalen.se/Sighting/136876428</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130839401</v>
+        <v>130300852</v>
       </c>
       <c r="B61" t="n">
-        <v>83307</v>
+        <v>75300</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7855,13 +7838,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445781</v>
+        <v>445737</v>
       </c>
       <c r="R61" t="n">
-        <v>7026373</v>
+        <v>7026346</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7885,27 +7868,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7931,38 +7914,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839401</t>
+          <t>https://artportalen.se/Sighting/130300852</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130301690</v>
+        <v>130837541</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>75300</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7972,13 +7955,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445682</v>
+        <v>445740</v>
       </c>
       <c r="R62" t="n">
-        <v>7026217</v>
+        <v>7026322</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8002,27 +7985,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal sumpgranskog</t>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8033,21 +8016,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8057,22 +8025,22 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301690</t>
+          <t>https://artportalen.se/Sighting/130837541</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130301915</v>
+        <v>130301741</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8080,21 +8048,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8104,13 +8072,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445762</v>
+        <v>445718</v>
       </c>
       <c r="R63" t="n">
-        <v>7026257</v>
+        <v>7026281</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8139,7 +8107,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8149,12 +8117,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8174,44 +8142,44 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301915</t>
+          <t>https://artportalen.se/Sighting/130301741</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130839069</v>
+        <v>130302583</v>
       </c>
       <c r="B64" t="n">
-        <v>79583</v>
+        <v>83307</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8221,10 +8189,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445706</v>
+        <v>445687</v>
       </c>
       <c r="R64" t="n">
-        <v>7026203</v>
+        <v>7026235</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8251,27 +8219,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8297,38 +8265,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839069</t>
+          <t>https://artportalen.se/Sighting/130302583</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130301523</v>
+        <v>130837316</v>
       </c>
       <c r="B65" t="n">
-        <v>80460</v>
+        <v>83307</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8338,13 +8306,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445674</v>
+        <v>445777</v>
       </c>
       <c r="R65" t="n">
-        <v>7026247</v>
+        <v>7026331</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8368,27 +8336,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8408,44 +8376,44 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301523</t>
+          <t>https://artportalen.se/Sighting/130837316</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130301748</v>
+        <v>130837548</v>
       </c>
       <c r="B66" t="n">
-        <v>80461</v>
+        <v>83307</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8455,13 +8423,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445681</v>
+        <v>445740</v>
       </c>
       <c r="R66" t="n">
-        <v>7026210</v>
+        <v>7026322</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8485,27 +8453,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8525,22 +8493,22 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301748</t>
+          <t>https://artportalen.se/Sighting/130837548</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131074382</v>
+        <v>130838158</v>
       </c>
       <c r="B67" t="n">
-        <v>58057</v>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8548,46 +8516,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445791</v>
+        <v>445638</v>
       </c>
       <c r="R67" t="n">
-        <v>7026340</v>
+        <v>7026382</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8611,27 +8570,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Lockade i ca 3 minuter på en grantopp</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog, nära källa</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8646,79 +8605,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131074382</t>
+          <t>https://artportalen.se/Sighting/130838158</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130303489</v>
+        <v>130839071</v>
       </c>
       <c r="B68" t="n">
-        <v>99118</v>
+        <v>83307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445824</v>
+        <v>445706</v>
       </c>
       <c r="R68" t="n">
-        <v>7026381</v>
+        <v>7026203</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8742,27 +8687,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8782,61 +8727,47 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303489</t>
+          <t>https://artportalen.se/Sighting/130839071</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130303691</v>
+        <v>130839401</v>
       </c>
       <c r="B69" t="n">
-        <v>99118</v>
+        <v>83307</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
@@ -8846,7 +8777,7 @@
         <v>445781</v>
       </c>
       <c r="R69" t="n">
-        <v>7026394</v>
+        <v>7026373</v>
       </c>
       <c r="S69" t="n">
         <v>7</v>
@@ -8873,27 +8804,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8913,71 +8844,57 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303691</t>
+          <t>https://artportalen.se/Sighting/130839401</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130303722</v>
+        <v>130301690</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445791</v>
+        <v>445682</v>
       </c>
       <c r="R70" t="n">
-        <v>7026379</v>
+        <v>7026217</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9009,7 +8926,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9019,12 +8936,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9035,6 +8952,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,44 +8976,44 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303722</t>
+          <t>https://artportalen.se/Sighting/130301690</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130301555</v>
+        <v>130301915</v>
       </c>
       <c r="B71" t="n">
-        <v>98030</v>
+        <v>80432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221063</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9091,13 +9023,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445699</v>
+        <v>445762</v>
       </c>
       <c r="R71" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9126,7 +9058,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9136,12 +9068,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9156,27 +9088,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130301555</t>
+          <t>https://artportalen.se/Sighting/130301915</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130302646</v>
+        <v>130839069</v>
       </c>
       <c r="B72" t="n">
-        <v>98030</v>
+        <v>79583</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9184,21 +9116,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221063</v>
+        <v>6459</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9208,10 +9140,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445702</v>
+        <v>445706</v>
       </c>
       <c r="R72" t="n">
-        <v>7026205</v>
+        <v>7026203</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9238,27 +9170,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På död gren på gammal levande gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9284,16 +9216,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302646</t>
+          <t>https://artportalen.se/Sighting/130839069</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130300536</v>
+        <v>130301523</v>
       </c>
       <c r="B73" t="n">
-        <v>97983</v>
+        <v>80460</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9301,21 +9233,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9325,10 +9257,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445736</v>
+        <v>445674</v>
       </c>
       <c r="R73" t="n">
-        <v>7026373</v>
+        <v>7026247</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9360,7 +9292,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9370,7 +9302,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -9395,60 +9327,65 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300536</t>
+          <t>https://artportalen.se/Sighting/130301523</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130302398</v>
+        <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>78339</v>
+        <v>80595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445681</v>
+        <v>445795</v>
       </c>
       <c r="R74" t="n">
-        <v>7026315</v>
+        <v>7026397</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9472,27 +9409,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9507,49 +9439,49 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130302398</t>
+          <t>https://artportalen.se/Sighting/136876693</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130303129</v>
+        <v>130301748</v>
       </c>
       <c r="B75" t="n">
-        <v>78339</v>
+        <v>80461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9559,10 +9491,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445734</v>
+        <v>445681</v>
       </c>
       <c r="R75" t="n">
-        <v>7026229</v>
+        <v>7026210</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9594,7 +9526,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9604,12 +9536,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9629,22 +9561,22 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303129</t>
+          <t>https://artportalen.se/Sighting/130301748</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130303406</v>
+        <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>78339</v>
+        <v>58008</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9652,37 +9584,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445827</v>
+        <v>445682</v>
       </c>
       <c r="R76" t="n">
-        <v>7026371</v>
+        <v>7026343</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9706,27 +9643,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9741,27 +9678,27 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130303406</t>
+          <t>https://artportalen.se/Sighting/136876106</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130719785</v>
+        <v>131074382</v>
       </c>
       <c r="B77" t="n">
-        <v>78339</v>
+        <v>58057</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9769,37 +9706,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445739</v>
+        <v>445791</v>
       </c>
       <c r="R77" t="n">
-        <v>7026240</v>
+        <v>7026340</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9823,27 +9769,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Lockade i ca 3 minuter på en grantopp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9858,49 +9804,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130719785</t>
+          <t>https://artportalen.se/Sighting/131074382</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130837438</v>
+        <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>78339</v>
+        <v>108448</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>220102</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9910,13 +9856,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445741</v>
+        <v>445723</v>
       </c>
       <c r="R78" t="n">
-        <v>7026328</v>
+        <v>7026207</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9940,27 +9886,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9975,49 +9916,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130837438</t>
+          <t>https://artportalen.se/Sighting/136875895</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130838077</v>
+        <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>78339</v>
+        <v>108448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228579</v>
+        <v>220102</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10027,13 +9968,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445709</v>
+        <v>445645</v>
       </c>
       <c r="R79" t="n">
-        <v>7026369</v>
+        <v>7026372</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10057,27 +9998,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (ca 200 år, 15 cm dbh) i gammal barrblandskog</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10092,65 +10028,79 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130838077</t>
+          <t>https://artportalen.se/Sighting/136876295</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130839076</v>
+        <v>130303489</v>
       </c>
       <c r="B80" t="n">
-        <v>78339</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445706</v>
+        <v>445824</v>
       </c>
       <c r="R80" t="n">
-        <v>7026203</v>
+        <v>7026381</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10174,27 +10124,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10214,47 +10164,61 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839076</t>
+          <t>https://artportalen.se/Sighting/130303489</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130839413</v>
+        <v>130303691</v>
       </c>
       <c r="B81" t="n">
-        <v>78339</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
@@ -10264,7 +10228,7 @@
         <v>445781</v>
       </c>
       <c r="R81" t="n">
-        <v>7026373</v>
+        <v>7026394</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -10291,27 +10255,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10331,57 +10295,71 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130839413</t>
+          <t>https://artportalen.se/Sighting/130303691</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130300281</v>
+        <v>130303722</v>
       </c>
       <c r="B82" t="n">
-        <v>79350</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445810</v>
+        <v>445791</v>
       </c>
       <c r="R82" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10413,7 +10391,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10423,12 +10401,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gren på gammal levande gran i gammal (150+) granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10448,44 +10426,44 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130300281</t>
+          <t>https://artportalen.se/Sighting/130303722</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130303411</v>
+        <v>130301555</v>
       </c>
       <c r="B83" t="n">
-        <v>79350</v>
+        <v>98030</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>260591</v>
+        <v>221063</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10495,10 +10473,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445827</v>
+        <v>445699</v>
       </c>
       <c r="R83" t="n">
-        <v>7026371</v>
+        <v>7026231</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10530,7 +10508,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10540,12 +10518,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10565,11 +10543,1527 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301555</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>130302646</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>445702</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7026205</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302646</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>130300536</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>445736</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300536</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130302398</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>445681</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7026315</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302398</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130303129</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>445734</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7026229</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303129</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>130303406</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>445827</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7026371</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303406</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>130719785</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>445739</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7026240</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719785</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130837438</v>
+      </c>
+      <c r="B90" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>445741</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7026328</v>
+      </c>
+      <c r="S90" t="n">
+        <v>6</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837438</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>130838077</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>445709</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7026369</v>
+      </c>
+      <c r="S91" t="n">
+        <v>6</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 200 år, 15 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838077</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>130839076</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>445706</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7026203</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839076</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>130839413</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>445781</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S93" t="n">
+        <v>7</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839413</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>136876331</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78485</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>445631</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7026386</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876331</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130300281</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>445810</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På gren på gammal levande gran i gammal (150+) granskog</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300281</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130303411</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>445827</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7026371</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130303411</t>
         </is>
@@ -10659,6 +12153,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78487</v>
+        <v>78488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78488</v>
+        <v>78490</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78490</v>
+        <v>78493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78493</v>
+        <v>78506</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -9368,11 +9368,7 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
@@ -9602,11 +9598,7 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108486</v>
+        <v>108491</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108486</v>
+        <v>108491</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108491</v>
+        <v>108512</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108491</v>
+        <v>108512</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108512</v>
+        <v>108513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108512</v>
+        <v>108513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108513</v>
+        <v>108518</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108513</v>
+        <v>108518</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108518</v>
+        <v>108521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108518</v>
+        <v>108521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>136876106</v>
       </c>
       <c r="B76" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108521</v>
+        <v>108527</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108521</v>
+        <v>108527</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108527</v>
+        <v>108528</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108527</v>
+        <v>108528</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108528</v>
+        <v>108540</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108528</v>
+        <v>108540</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>136876232</v>
       </c>
       <c r="B7" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>136875897</v>
       </c>
       <c r="B14" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136875941</v>
       </c>
       <c r="B15" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>136876113</v>
       </c>
       <c r="B16" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136876614</v>
       </c>
       <c r="B17" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136876260</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136876308</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>136876428</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>136876693</v>
       </c>
       <c r="B74" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136875895</v>
       </c>
       <c r="B78" t="n">
-        <v>108540</v>
+        <v>108541</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>136876295</v>
       </c>
       <c r="B79" t="n">
-        <v>108540</v>
+        <v>108541</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>136876331</v>
       </c>
       <c r="B94" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
